--- a/site/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/headings.xlsx
+++ b/site/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,154 +463,418 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+          <t>h_01KM3CXQA4DAT4CM7WKSDCR1M0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KM3CXQA4DAT4CM7WKSDCR1M0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Key Features</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>h_01KM3CZ17J4YZFFPE23N25VKCA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KM3CZ17J4YZFFPE23N25VKCA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Set Up Integration Parameters</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Set Up Triggers</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01JNGB3B2RMJQ844VPCVP4AKSS</t>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01JNGB3B2RMJQ844VPCVP4AKSS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Run the Integration</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01J0JG38N49DASPBXSDBN4QDMQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Download CSV Report</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Operational Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KAGE0X6XX6CWRTJFB7VBCGJS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KAGE0X6XX6CWRTJFB7VBCGJS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KM3D7AP4C9XJTXJVADEBQBZ9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KM3D7AP4C9XJTXJVADEBQBZ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Oracle HCM Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KM3DC3MVD3K2Z773738TRRYM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KM3DC3MVD3K2Z773738TRRYM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Active Directory Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KM3DGHP77BVZV5HF4PQPV1TR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KM3DGHP77BVZV5HF4PQPV1TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KM3DK6SRPF6T129J6A3MD4KD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KM3DK6SRPF6T129J6A3MD4KD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KM3DPDM9VP6BH6N420HKW9E1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KM3DPDM9VP6BH6N420HKW9E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KM3E25PHC9KYYR4FEN3BT8DM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KM3E25PHC9KYYR4FEN3BT8DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KM3E25PNWGKMFBNDK6BKC99D</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01KM3E25PNWGKMFBNDK6BKC99D</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>h_01JPMEDG8C4C3GS46HWAAWBBV4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01JPMEDG8C4C3GS46HWAAWBBV4</t>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Oracle-Cloud-HCM-to-Active-Directory-User-Reconciliation/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
